--- a/backend/src/main/resources/templates/temple-lead.xlsx
+++ b/backend/src/main/resources/templates/temple-lead.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="CI" sheetId="30" r:id="rId1"/>
@@ -162,12 +162,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>ACCOUNT NAME</t>
     </r>
     <r>
@@ -186,7 +180,8 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>NINGBO LIDE TECHNOLOGY CO.,LTD.                                                                                                  ADDRESS</t>
+      <t>NINGBO LIDE TECHNOLOGY CO.,LTD.                                                                                                  
+ADDRESS</t>
     </r>
     <r>
       <rPr>
@@ -204,7 +199,9 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>Xiufeng, Gaoqiao Town, Haishu District, Ningbo, Zhejiang                                                                                               BANK NAME : BANK OF CHINA , NINGBO GAOQIAO SUB-BRANCH                                                                             BANK ADDRESS</t>
+      <t>Xiufeng, Gaoqiao Town, Haishu District, Ningbo, Zhejiang                                                                                               
+BANK NAME : BANK OF CHINA , NINGBO GAOQIAO SUB-BRANCH                                                                             
+BANK ADDRESS</t>
     </r>
     <r>
       <rPr>
@@ -222,7 +219,8 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">221, 223 LIAN FENG ZHONG ROAD, NINGBO CITY, ZHEJIANG, CHINA                                                BANK ACCOUNT NO.: 402686490492
+      <t xml:space="preserve">221, 223 LIAN FENG ZHONG ROAD, NINGBO CITY, ZHEJIANG, CHINA                                                
+BANK ACCOUNT NO.: 402686490492
 SWIFT CODE: BKCHCNBJ92A      </t>
     </r>
   </si>
@@ -582,14 +580,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1214,7 +1212,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1438,6 +1436,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1513,15 +1526,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>503555</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>118745</xdr:rowOff>
+      <xdr:colOff>480695</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>50165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
+      <xdr:colOff>739140</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>607060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1538,7 +1551,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3769995" y="6957060"/>
+          <a:off x="3747135" y="7437120"/>
           <a:ext cx="2326005" cy="2019935"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2125,120 +2138,120 @@
       <c r="A20" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="76"/>
     </row>
     <row r="21" customHeight="1" spans="1:7">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46"/>
+      <c r="A21" s="74"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="76"/>
     </row>
     <row r="22" customHeight="1" spans="1:7">
-      <c r="A22" s="44"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="76"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46"/>
+      <c r="A23" s="74"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="76"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="76"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="76"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46"/>
+      <c r="A26" s="74"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="76"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="44"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="76"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="44"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="76"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="44"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="76"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="44"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="76"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="44"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="46"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="47"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="76"/>
+    </row>
+    <row r="32" ht="64" customHeight="1" spans="1:7">
+      <c r="A32" s="77"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="12">
